--- a/api/clv3/xlsx/fr/UNSDG-Indicators.xlsx
+++ b/api/clv3/xlsx/fr/UNSDG-Indicators.xlsx
@@ -1066,7 +1066,7 @@
     <t>10.4.2</t>
   </si>
   <si>
-    <t>Effet redistributif de la politique budgétaire2</t>
+    <t>Effet redistributif de la politique budgétaire</t>
   </si>
   <si>
     <t>10.5.1</t>
@@ -1843,7 +1843,7 @@
     <t>17.6.1</t>
   </si>
   <si>
-    <t>Abonnements à une connexion à Internet à haut débit fixe pour 100 habitants, par vitesse de connexion5</t>
+    <t>Abonnements à une connexion à Internet à haut débit fixe pour 100 habitants, par vitesse de connexion</t>
   </si>
   <si>
     <t>17.6</t>
